--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445764C4-087C-4F61-9C5A-ACD385AE3C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF2BD3-7E73-43BA-B051-2BFA50C3E1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 19-12-2025'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF2BD3-7E73-43BA-B051-2BFA50C3E1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5558BF12-63A4-4E45-A446-878BB7BEDCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 02-02-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5558BF12-63A4-4E45-A446-878BB7BEDCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36640992-6353-4051-8FB9-B5C9E2A635ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 02-02-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 20-02-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -542,9 +542,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -599,7 +599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -640,7 +640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -681,7 +681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -736,7 +736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -777,7 +777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -808,7 +808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -849,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -872,7 +872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -895,7 +895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -912,7 +912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -926,7 +926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -940,7 +940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -954,7 +954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -968,7 +968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -982,7 +982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36640992-6353-4051-8FB9-B5C9E2A635ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8932AF8-BA47-41DE-8E60-645217FB6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 20-02-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 04-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8932AF8-BA47-41DE-8E60-645217FB6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577187A7-D77F-4762-BB24-0DC7F8ACE4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 04-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 06-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577187A7-D77F-4762-BB24-0DC7F8ACE4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52FAC82-43CC-4243-A670-5D8BBA89CED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52FAC82-43CC-4243-A670-5D8BBA89CED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE1C88B-D4BE-435E-BE67-872E81A6D358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE1C88B-D4BE-435E-BE67-872E81A6D358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC3A222-01D3-4001-85EA-5A8FA9A8E591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 06-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 09-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC3A222-01D3-4001-85EA-5A8FA9A8E591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D67124-1B73-4102-8ED9-AC67D94F74B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D67124-1B73-4102-8ED9-AC67D94F74B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA82C01-41DE-48DC-B8A1-25606A894E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 09-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 11-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA82C01-41DE-48DC-B8A1-25606A894E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7BC1F9-0C07-42CF-9698-74A48067C9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7BC1F9-0C07-42CF-9698-74A48067C9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D2F84E-0D77-497F-A303-6765F20C0389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 11-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 20-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D2F84E-0D77-497F-A303-6765F20C0389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A5AC0-D5E0-45AF-AA8D-0CA73BB40997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 20-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 25-03-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A5AC0-D5E0-45AF-AA8D-0CA73BB40997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85ED656D-05C0-4F0D-8139-E1CEB13841AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 25-03-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 08-04-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85ED656D-05C0-4F0D-8139-E1CEB13841AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F4E79-9694-469D-AC8E-AC47B0B5EC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 08-04-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 10-04-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F4E79-9694-469D-AC8E-AC47B0B5EC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF45B90-7C60-4046-A81F-67F88128620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF45B90-7C60-4046-A81F-67F88128620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F15AC-353C-43B7-A729-B32BBA81B316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 10-04-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 14-04-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F15AC-353C-43B7-A729-B32BBA81B316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BE3639-DBA9-438E-8868-A06EA8708E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 14-04-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 24-04-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BE3639-DBA9-438E-8868-A06EA8708E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABF16E7-9482-4BD9-954C-7B1B6CE2CE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABF16E7-9482-4BD9-954C-7B1B6CE2CE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54E7CB7-9D2E-4137-A09F-5B58B77F6419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 24-04-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 27-04-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54E7CB7-9D2E-4137-A09F-5B58B77F6419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3228255-4FA6-41D9-A84E-6F673A5ADC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 27-04-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 06-05-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3228255-4FA6-41D9-A84E-6F673A5ADC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D7C712-5092-471E-87D7-3D5AC185398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 06-05-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 01-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D7C712-5092-471E-87D7-3D5AC185398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB5181-1535-418C-94E4-A441FD44CE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 01-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 02-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB5181-1535-418C-94E4-A441FD44CE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDB76B7-0329-474F-8428-90C338EFFFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDB76B7-0329-474F-8428-90C338EFFFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26937A0-C935-4ECE-8EAF-0E145817C17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 02-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 05-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF2BD3-7E73-43BA-B051-2BFA50C3E1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71EC0B7-1379-472D-B681-53AEF13E55E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71EC0B7-1379-472D-B681-53AEF13E55E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354F770B-5F7E-4EBE-B0B5-64B6453890DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 29-01-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 09-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354F770B-5F7E-4EBE-B0B5-64B6453890DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709F549D-1408-43C3-BE67-D47462CDC6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709F549D-1408-43C3-BE67-D47462CDC6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B778B83B-4E00-4E80-A665-FBE63FA9A6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B778B83B-4E00-4E80-A665-FBE63FA9A6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48009B37-B6AA-4342-A5F1-72D7CFF23C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 09-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 15-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -542,9 +542,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -599,7 +599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -640,7 +640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -681,7 +681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -736,7 +736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -777,7 +777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -808,7 +808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -849,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -872,7 +872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -895,7 +895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -912,7 +912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -926,7 +926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -940,7 +940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -954,7 +954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -968,7 +968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -982,7 +982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48009B37-B6AA-4342-A5F1-72D7CFF23C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5E5E3A-F0C4-49D2-8F90-55F73F5CCD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 15-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5E5E3A-F0C4-49D2-8F90-55F73F5CCD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD387DFE-FE0E-408E-BB50-B988FDAE8233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -542,9 +542,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -599,7 +599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -640,7 +640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -681,7 +681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -736,7 +736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -777,7 +777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -808,7 +808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -849,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -872,7 +872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -895,7 +895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -912,7 +912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -926,7 +926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -940,7 +940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -954,7 +954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -968,7 +968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -982,7 +982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>57</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD387DFE-FE0E-408E-BB50-B988FDAE8233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239A3D15-CE1B-46BB-96BC-31AE221E457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5E5E3A-F0C4-49D2-8F90-55F73F5CCD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AACCB84-5151-44C5-A23D-4FC00E0BF7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 22-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AACCB84-5151-44C5-A23D-4FC00E0BF7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672DC7D-4298-414A-8654-67668CE47BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 23-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 25-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672DC7D-4298-414A-8654-67668CE47BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B375A9-6660-481E-A427-4664A73D233E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 25-06-2026'!$A$1:$M$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 30-06-2026'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="60">
   <si>
     <t>Standard</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>DIS91 (D9134L)</t>
+  </si>
+  <si>
+    <t>Test mangler</t>
   </si>
   <si>
     <t>Sygehushenvisning</t>
@@ -759,7 +762,7 @@
         <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -779,16 +782,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -796,24 +799,24 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -831,7 +834,7 @@
         <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -851,10 +854,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -874,33 +877,33 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -909,15 +912,15 @@
         <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -928,10 +931,10 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -942,10 +945,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -956,10 +959,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -976,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L18" t="s">
         <v>16</v>
@@ -984,13 +987,13 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
@@ -1031,7 +1034,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
@@ -1072,7 +1075,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
@@ -1110,7 +1113,7 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
@@ -1125,7 +1128,7 @@
         <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -1145,13 +1148,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
@@ -1166,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
         <v>16</v>
@@ -1186,27 +1189,27 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -1217,13 +1220,13 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
         <v>16</v>
@@ -1231,13 +1234,13 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" t="s">
         <v>16</v>
@@ -1245,13 +1248,13 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" t="s">
         <v>16</v>
@@ -1259,13 +1262,13 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
         <v>16</v>
@@ -1273,13 +1276,13 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
         <v>16</v>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAFC142-02B2-42E0-8F87-E77DDA58E17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DAE22A-5A3D-4024-8336-B57E295811E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 30-06-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DAE22A-5A3D-4024-8336-B57E295811E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86DBE7F-5CD5-41C0-957A-62F9AD8CB0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 02-07-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DAE22A-5A3D-4024-8336-B57E295811E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0054F09A-3B75-48FB-9138-40588E2E3177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 01-07-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86DBE7F-5CD5-41C0-957A-62F9AD8CB0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523F16CA-DD7F-4E21-BD5F-EE8A49FB0E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 02-07-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523F16CA-DD7F-4E21-BD5F-EE8A49FB0E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86103891-6884-4268-BCFA-51DF6485EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 03-07-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 09-07-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86103891-6884-4268-BCFA-51DF6485EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E582E16B-1203-41BC-BCB1-15BB90096EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 09-07-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 19-08-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E582E16B-1203-41BC-BCB1-15BB90096EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87D0904-8A02-4767-8348-D521D2BE7175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 19-08-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 21-08-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87D0904-8A02-4767-8348-D521D2BE7175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A05218-016E-4692-9B79-302848E71F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 21-08-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 27-08-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A05218-016E-4692-9B79-302848E71F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C175A80-EA4A-411B-8C6E-D23FF7E91BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 27-08-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 02-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C175A80-EA4A-411B-8C6E-D23FF7E91BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB5DB23-1B29-4C5F-AB6C-48EFC9DCC57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 02-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 06-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB5DB23-1B29-4C5F-AB6C-48EFC9DCC57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A74760C-BC6C-455D-89DC-D47E231AE852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A74760C-BC6C-455D-89DC-D47E231AE852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DDCECF-0425-4C72-A4C1-B49B65A1F58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 06-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 07-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DDCECF-0425-4C72-A4C1-B49B65A1F58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C20BEF-B33C-46AD-9628-87989ED75845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 07-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 09-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C20BEF-B33C-46AD-9628-87989ED75845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DC7FC2-C234-4561-98B5-B71B93D6A76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
